--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T42" s="9" t="n">
         <v>0</v>
@@ -5406,13 +5406,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5454,7 +5454,7 @@
         <v>4</v>
       </c>
       <c r="W46" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>7</v>
@@ -10611,7 +10611,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10625,13 +10625,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10669,8 +10669,8 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>3</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
@@ -15373,7 +15373,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,11 @@
       <c r="AB3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="4" t="inlineStr"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -3310,7 +3314,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3718,7 +3726,11 @@
       <c r="AB29" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4651,7 +4663,11 @@
       <c r="AB38" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC38" s="4" t="inlineStr"/>
+      <c r="AC38" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5471,7 +5487,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -6190,7 +6210,11 @@
       <c r="AB53" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6291,7 +6315,11 @@
       <c r="AB54" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -6392,7 +6420,11 @@
       <c r="AB55" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC55" s="4" t="inlineStr"/>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6901,7 +6933,11 @@
       <c r="AB60" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -7309,7 +7345,11 @@
       <c r="AB64" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC64" s="4" t="inlineStr"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -7410,7 +7450,11 @@
       <c r="AB65" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC65" s="4" t="inlineStr"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -8022,7 +8066,11 @@
       <c r="AB71" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC71" s="4" t="inlineStr"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8228,7 +8276,11 @@
       <c r="AB73" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC73" s="4" t="inlineStr"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -8955,7 +9007,11 @@
       <c r="AB80" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -10997,7 +11053,11 @@
       <c r="AB100" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC100" s="4" t="inlineStr"/>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11203,7 +11263,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11914,7 +11978,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12221,7 +12289,11 @@
       <c r="AB112" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12322,7 +12394,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12633,7 +12709,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -13251,7 +13331,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13453,7 +13537,11 @@
       <c r="AB124" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -12,8 +12,8 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$136</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 45 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 37 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC136"/>
+  <dimension ref="A1:AC137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1750,8 +1750,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y14" s="9" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>10</v>
@@ -2679,8 +2679,8 @@
       <c r="Y19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z19" s="9" t="n">
-        <v>0</v>
+      <c r="Z19" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA19" s="10" t="n">
         <v>1</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2754,8 +2754,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P20" s="9" t="n">
-        <v>3</v>
+      <c r="P20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q20" s="10" t="n">
         <v>2</v>
@@ -4374,7 +4374,7 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4444,8 +4444,8 @@
       <c r="Y36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z36" s="9" t="n">
-        <v>0</v>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA36" s="10" t="n">
         <v>1</v>
@@ -5929,7 +5929,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5999,8 +5999,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -6175,7 +6175,7 @@
         <v>2</v>
       </c>
       <c r="Q53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="9" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6277,10 +6277,10 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="9" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q54" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -7074,17 +7074,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7231,8 +7231,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7795,13 +7795,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -8136,13 +8136,13 @@
         <v>1</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S72" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" s="9" t="n">
         <v>0</v>
@@ -8197,7 +8197,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8249,8 +8249,8 @@
       <c r="S73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T73" s="9" t="n">
-        <v>0</v>
+      <c r="T73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U73" s="9" t="n">
         <v>0</v>
@@ -8911,24 +8911,24 @@
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>2175</v>
+        <v>28680117</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Bossuet Gaveliers Toastmasters Club</t>
+          <t>Impact Toastmasters</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8942,13 +8942,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
@@ -8987,31 +8987,25 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X80" s="10" t="n">
-        <v>4</v>
+      <c r="X80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="10" t="n">
-        <v>1</v>
+      <c r="Z80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB80" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC80" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB80" s="4" t="n"/>
+      <c r="AC80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -9025,11 +9019,11 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>491</v>
+        <v>2175</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Green Heart Club</t>
+          <t>Bossuet Gaveliers Toastmasters Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
@@ -9047,10 +9041,10 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K81" s="4" t="n">
         <v>1</v>
@@ -9083,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
@@ -9110,11 +9104,11 @@
         <v>1</v>
       </c>
       <c r="AB81" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC81" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -9130,11 +9124,11 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>5429561</v>
+        <v>491</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Have Your Say</t>
+          <t>Green Heart Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -9152,17 +9146,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L82" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M82" s="7" t="n">
@@ -9188,7 +9182,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T82" s="9" t="n">
         <v>0</v>
@@ -9202,8 +9196,8 @@
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X82" s="9" t="n">
-        <v>3</v>
+      <c r="X82" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -9215,9 +9209,13 @@
         <v>1</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC82" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC82" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -9231,15 +9229,15 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>921076</v>
+        <v>5429561</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Sprich to Me</t>
+          <t>Have Your Say</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -9253,13 +9251,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="8" t="inlineStr">
         <is>
@@ -9298,25 +9296,25 @@
         <v>0</v>
       </c>
       <c r="V83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="10" t="n">
-        <v>6</v>
+      <c r="X83" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC83" s="4" t="inlineStr"/>
     </row>
@@ -9332,11 +9330,11 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>4145151</v>
+        <v>921076</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>State Street Tales</t>
+          <t>Sprich to Me</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -9354,17 +9352,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L84" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="7" t="n">
@@ -9404,8 +9402,8 @@
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="9" t="n">
-        <v>3</v>
+      <c r="X84" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
@@ -9429,19 +9427,19 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>7709093</v>
+        <v>4145151</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Club Des Orateurs De Strasbourg</t>
+          <t>State Street Tales</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9455,10 +9453,10 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
         <v>0</v>
@@ -9506,19 +9504,19 @@
         <v>0</v>
       </c>
       <c r="X85" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB85" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC85" s="4" t="inlineStr"/>
     </row>
@@ -9534,11 +9532,11 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7067</v>
+        <v>7709093</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Les Orateurs De Luxembourg</t>
+          <t>Club Des Orateurs De Strasbourg</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -9556,17 +9554,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L86" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M86" s="7" t="n">
@@ -9601,13 +9599,13 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X86" s="10" t="n">
-        <v>5</v>
+      <c r="X86" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
@@ -9619,7 +9617,7 @@
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC86" s="4" t="inlineStr"/>
     </row>
@@ -9635,15 +9633,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>5032586</v>
+        <v>7067</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Les Orateurs de Thionville</t>
+          <t>Les Orateurs De Luxembourg</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9657,13 +9655,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="8" t="inlineStr">
         <is>
@@ -9702,25 +9700,25 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>0</v>
+      <c r="X87" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC87" s="4" t="inlineStr"/>
     </row>
@@ -9736,11 +9734,11 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>834396</v>
+        <v>5032586</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Metzmerising Toastmasters Club</t>
+          <t>Les Orateurs de Thionville</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
@@ -9758,10 +9756,10 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J88" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K88" s="4" t="n">
         <v>0</v>
@@ -9809,7 +9807,7 @@
         <v>0</v>
       </c>
       <c r="X88" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
@@ -9833,15 +9831,15 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>28675493</v>
+        <v>834396</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>BIL Public Speakers</t>
+          <t>Metzmerising Toastmasters Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -9859,10 +9857,10 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K89" s="4" t="n">
         <v>0</v>
@@ -9910,7 +9908,7 @@
         <v>0</v>
       </c>
       <c r="X89" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9922,7 +9920,7 @@
         <v>1</v>
       </c>
       <c r="AB89" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC89" s="4" t="inlineStr"/>
     </row>
@@ -9938,11 +9936,11 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>858404</v>
+        <v>28675493</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Casemates Communicators Luxembourg</t>
+          <t>BIL Public Speakers</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -9960,10 +9958,10 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0</v>
@@ -9996,7 +9994,7 @@
         <v>0</v>
       </c>
       <c r="S90" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T90" s="9" t="n">
         <v>0</v>
@@ -10010,8 +10008,8 @@
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X90" s="10" t="n">
-        <v>5</v>
+      <c r="X90" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -10023,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC90" s="4" t="inlineStr"/>
     </row>
@@ -10039,15 +10037,15 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2187867</v>
+        <v>858404</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>EIB Toastmasters Club</t>
+          <t>Casemates Communicators Luxembourg</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10061,17 +10059,17 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L91" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M91" s="7" t="n">
@@ -10097,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10106,31 +10104,27 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X91" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="10" t="n">
-        <v>1</v>
+      <c r="Z91" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC91" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -10144,11 +10138,11 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>7208895</v>
+        <v>2187867</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Pitch Craft For Entrepreneurs Toastmasters</t>
+          <t>EIB Toastmasters Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -10166,13 +10160,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10202,7 +10196,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -10211,29 +10205,29 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y92" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA92" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB92" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y92" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z92" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA92" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB92" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="AC92" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -10245,19 +10239,19 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>6286</v>
+        <v>7208895</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Agora 75 Club</t>
+          <t>Pitch Craft For Entrepreneurs Toastmasters</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -10271,13 +10265,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10300,8 +10294,8 @@
       <c r="P93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" s="10" t="n">
-        <v>2</v>
+      <c r="Q93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R93" s="9" t="n">
         <v>0</v>
@@ -10309,20 +10303,20 @@
       <c r="S93" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T93" s="10" t="n">
-        <v>1</v>
+      <c r="T93" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -10334,11 +10328,11 @@
         <v>1</v>
       </c>
       <c r="AB93" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC93" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -10354,15 +10348,15 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>7955657</v>
+        <v>6286</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Ateme Toastmasters</t>
+          <t>Agora 75 Club</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10376,17 +10370,17 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M94" s="7" t="n">
@@ -10405,23 +10399,23 @@
       <c r="P94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" s="9" t="n">
-        <v>0</v>
+      <c r="Q94" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S94" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10438,8 +10432,14 @@
       <c r="AA94" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB94" s="4" t="n"/>
-      <c r="AC94" s="4" t="inlineStr"/>
+      <c r="AB94" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC94" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -10453,15 +10453,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>6631</v>
+        <v>7955657</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Forum des Rives de Seine</t>
+          <t>Ateme Toastmasters</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10475,17 +10475,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L95" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -10519,15 +10519,15 @@
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V95" s="10" t="n">
+      <c r="V95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W95" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X95" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
@@ -10537,9 +10537,7 @@
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB95" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="AB95" s="4" t="n"/>
       <c r="AC95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
@@ -10554,15 +10552,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1575</v>
+        <v>6631</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters 75</t>
+          <t>Forum des Rives de Seine</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10576,13 +10574,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
@@ -10614,20 +10612,20 @@
       <c r="S96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T96" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U96" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V96" s="9" t="n">
-        <v>0</v>
+      <c r="T96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X96" s="9" t="n">
-        <v>3</v>
+      <c r="X96" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10639,13 +10637,9 @@
         <v>1</v>
       </c>
       <c r="AB96" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC96" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -10659,15 +10653,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>7776982</v>
+        <v>1575</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Polyglottes Paris</t>
+          <t>Toastmasters 75</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10681,13 +10675,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10708,7 +10702,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10719,20 +10713,20 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V97" s="10" t="n">
-        <v>4</v>
+      <c r="T97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="10" t="n">
-        <v>4</v>
+      <c r="X97" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10755,24 +10749,24 @@
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>7308562</v>
+        <v>7776982</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Den Haag Toastmasters</t>
+          <t>Toastmasters Polyglottes Paris</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10786,13 +10780,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10830,28 +10824,32 @@
       <c r="U98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V98" s="9" t="n">
-        <v>1</v>
+      <c r="V98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="9" t="n">
-        <v>3</v>
+      <c r="X98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB98" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC98" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -10865,15 +10863,15 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>1523749</v>
+        <v>7308562</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>International Toastmasters The Hague</t>
+          <t>Den Haag Toastmasters</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10887,17 +10885,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M99" s="7" t="n">
@@ -10923,22 +10921,22 @@
         <v>0</v>
       </c>
       <c r="S99" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T99" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T99" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W99" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X99" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10950,7 +10948,7 @@
         <v>1</v>
       </c>
       <c r="AB99" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC99" s="4" t="inlineStr"/>
     </row>
@@ -10966,15 +10964,15 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1550131</v>
+        <v>1523749</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Leiden Toastmasters</t>
+          <t>International Toastmasters The Hague</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10988,17 +10986,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L100" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="7" t="n">
@@ -11015,7 +11013,7 @@
         </is>
       </c>
       <c r="P100" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="9" t="n">
         <v>0</v>
@@ -11024,40 +11022,36 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T100" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U100" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V100" s="10" t="n">
-        <v>4</v>
+      <c r="U100" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="10" t="n">
-        <v>6</v>
+      <c r="X100" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="10" t="n">
-        <v>1</v>
+      <c r="Z100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC100" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11071,15 +11065,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>5501964</v>
+        <v>1550131</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>The Hague University Toastmasters</t>
+          <t>Leiden Toastmasters</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11093,17 +11087,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L101" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M101" s="7" t="n">
@@ -11120,7 +11114,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -11131,36 +11125,36 @@
       <c r="S101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" s="9" t="n">
-        <v>2</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V101" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="9" t="n">
-        <v>2</v>
+      <c r="X101" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC101" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -11176,11 +11170,11 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>620921</v>
+        <v>5501964</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of The Hague</t>
+          <t>The Hague University Toastmasters</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -11198,17 +11192,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L102" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -11225,31 +11219,31 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U102" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V102" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="10" t="n">
-        <v>6</v>
+      <c r="X102" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11261,11 +11255,11 @@
         <v>1</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC102" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -11277,19 +11271,19 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>28678723</v>
+        <v>620921</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>CC7 Europe Toastmasters</t>
+          <t>Toastmasters of The Hague</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -11303,17 +11297,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="L103" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -11330,7 +11324,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11348,27 +11342,31 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="9" t="n">
-        <v>3</v>
+      <c r="X103" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC103" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -11382,15 +11380,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>3697073</v>
+        <v>28678723</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>McDermott TM The Hague</t>
+          <t>CC7 Europe Toastmasters</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11404,13 +11402,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L104" s="8" t="inlineStr">
         <is>
@@ -11431,7 +11429,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -11449,25 +11447,25 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="10" t="n">
-        <v>4</v>
+      <c r="X104" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC104" s="4" t="inlineStr"/>
     </row>
@@ -11483,35 +11481,35 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>7632518</v>
+        <v>3697073</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Shell Toastmasters Club Rotterdam</t>
+          <t>McDermott TM The Hague</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J105" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K105" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F105" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G105" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H105" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I105" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J105" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K105" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -11532,10 +11530,10 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R105" s="9" t="n">
         <v>0</v>
@@ -11543,32 +11541,32 @@
       <c r="S105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T105" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U105" s="10" t="n">
-        <v>1</v>
+      <c r="T105" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="9" t="n">
-        <v>2</v>
+      <c r="X105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="9" t="n">
-        <v>0</v>
+      <c r="Z105" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC105" s="4" t="inlineStr"/>
     </row>
@@ -11584,15 +11582,15 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>3943870</v>
+        <v>7632518</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Shell Toastmasters The Hague Club</t>
+          <t>Shell Toastmasters Club Rotterdam</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -11609,10 +11607,10 @@
         <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11636,7 +11634,7 @@
         <v>0</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11644,32 +11642,32 @@
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" s="9" t="n">
-        <v>0</v>
+      <c r="T106" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="10" t="n">
-        <v>1</v>
+      <c r="Z106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC106" s="4" t="inlineStr"/>
     </row>
@@ -11685,15 +11683,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>28677998</v>
+        <v>3943870</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Swift Toastmasters</t>
+          <t>Shell Toastmasters The Hague Club</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11707,17 +11705,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L107" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="7" t="n">
@@ -11734,49 +11732,45 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q107" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB107" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB107" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC107" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -11790,15 +11784,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28677500</v>
+        <v>28677998</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Worley WeME Toastmaster</t>
+          <t>Swift Toastmasters</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11812,17 +11806,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L108" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="7" t="n">
@@ -11839,10 +11833,10 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R108" s="9" t="n">
         <v>0</v>
@@ -11857,7 +11851,7 @@
         <v>0</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
@@ -11869,15 +11863,19 @@
         <v>0</v>
       </c>
       <c r="Z108" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA108" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB108" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC108" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11887,19 +11885,19 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>7274025</v>
+        <v>28677500</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Den Bosch Toastmasters Club</t>
+          <t>Worley WeME Toastmaster</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11913,17 +11911,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="K109" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L109" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="7" t="n">
@@ -11940,10 +11938,10 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
@@ -11951,8 +11949,8 @@
       <c r="S109" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T109" s="10" t="n">
-        <v>1</v>
+      <c r="T109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U109" s="9" t="n">
         <v>0</v>
@@ -11963,8 +11961,8 @@
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="10" t="n">
-        <v>4</v>
+      <c r="X109" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11976,13 +11974,9 @@
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC109" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -11996,15 +11990,15 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>935413</v>
+        <v>7274025</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Rotterdam Toastmasters</t>
+          <t>Den Bosch Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12018,13 +12012,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -12045,10 +12039,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12056,21 +12050,21 @@
       <c r="S110" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T110" s="9" t="n">
-        <v>0</v>
+      <c r="T110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V110" s="10" t="n">
+      <c r="V110" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W110" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W110" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X110" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
@@ -12081,11 +12075,11 @@
         <v>1</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC110" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12101,15 +12095,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>28679394</v>
+        <v>935413</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>RSM Toastmasters Club</t>
+          <t>Rotterdam Toastmasters</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12123,13 +12117,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12159,7 +12153,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" s="9" t="n">
         <v>0</v>
@@ -12167,28 +12161,32 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" s="9" t="n">
-        <v>0</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W111" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X111" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC111" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC111" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -12202,15 +12200,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1994030</v>
+        <v>28679394</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Sprekershaven Toastmasters Rotterdam</t>
+          <t>RSM Toastmasters Club</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12224,13 +12222,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12269,31 +12267,27 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X112" s="10" t="n">
-        <v>5</v>
+      <c r="X112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="10" t="n">
-        <v>1</v>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12307,11 +12301,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>28678590</v>
+        <v>1994030</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Breda</t>
+          <t>Sprekershaven Toastmasters Rotterdam</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -12329,13 +12323,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12356,10 +12350,10 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12374,13 +12368,13 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12412,11 +12406,11 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>4386342</v>
+        <v>28678590</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Tilburg</t>
+          <t>Toastmasters Breda</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -12434,13 +12428,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12479,13 +12473,13 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12497,11 +12491,11 @@
         <v>1</v>
       </c>
       <c r="AB114" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC114" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12513,15 +12507,15 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>7930894</v>
+        <v>4386342</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>ASML Toastmasters</t>
+          <t>Toastmasters Tilburg</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -12539,13 +12533,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12566,7 +12560,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>1</v>
@@ -12577,36 +12571,36 @@
       <c r="S115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T115" s="10" t="n">
-        <v>1</v>
+      <c r="T115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC115" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -12622,15 +12616,15 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1071665</v>
+        <v>7930894</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Lighttown Speakers</t>
+          <t>ASML Toastmasters</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -12644,13 +12638,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12671,47 +12665,47 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q116" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q116" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="10" t="n">
-        <v>2</v>
+      <c r="S116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T116" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U116" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V116" s="10" t="n">
+      <c r="U116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="10" t="n">
-        <v>1</v>
+      <c r="Z116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -12727,15 +12721,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>777407</v>
+        <v>1071665</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Eindhoven</t>
+          <t>Lighttown Speakers</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12749,13 +12743,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12776,31 +12770,31 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="9" t="n">
-        <v>0</v>
+      <c r="S117" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T117" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V117" s="9" t="n">
-        <v>2</v>
+      <c r="U117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X117" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
@@ -12812,11 +12806,11 @@
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC117" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12832,15 +12826,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1933731</v>
+        <v>777407</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Maastricht</t>
+          <t>Toastmasters Eindhoven</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12854,13 +12848,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12890,22 +12884,22 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T118" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T118" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12928,24 +12922,24 @@
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>28677576</v>
+        <v>1933731</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Dell France Toastmasters</t>
+          <t>Toastmasters Maastricht</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12959,17 +12953,17 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K119" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L119" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M119" s="7" t="n">
@@ -12995,7 +12989,7 @@
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T119" s="9" t="n">
         <v>0</v>
@@ -13009,22 +13003,26 @@
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="9" t="n">
-        <v>2</v>
+      <c r="X119" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB119" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC119" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC119" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -13038,11 +13036,11 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28678280</v>
+        <v>28677576</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Bordeaux</t>
+          <t>Dell France Toastmasters</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -13060,17 +13058,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L120" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
@@ -13087,32 +13085,32 @@
         </is>
       </c>
       <c r="P120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W120" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W120" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
@@ -13123,13 +13121,9 @@
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13143,15 +13137,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>3365085</v>
+        <v>28678280</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Toulouse Speakers</t>
+          <t>Toastmasters Bordeaux</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13165,17 +13159,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L121" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
@@ -13192,10 +13186,10 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" s="9" t="n">
         <v>0</v>
@@ -13203,14 +13197,14 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="10" t="n">
-        <v>1</v>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -13221,8 +13215,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="10" t="n">
-        <v>1</v>
+      <c r="Z121" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -13230,7 +13224,11 @@
       <c r="AB121" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AC121" s="4" t="inlineStr"/>
+      <c r="AC121" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13244,15 +13242,15 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1095816</v>
+        <v>3365085</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Toulouse Toastmasters Communication</t>
+          <t>Toulouse Speakers</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13266,17 +13264,17 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L122" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L122" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
@@ -13293,16 +13291,16 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T122" s="10" t="n">
         <v>1</v>
@@ -13310,15 +13308,15 @@
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V122" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W122" s="10" t="n">
+      <c r="V122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="X122" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
       </c>
@@ -13329,13 +13327,9 @@
         <v>1</v>
       </c>
       <c r="AB122" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC122" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AC122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13345,19 +13339,19 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>3549525</v>
+        <v>1095816</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Lyon English Toastmasters</t>
+          <t>Toulouse Toastmasters Communication</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13371,17 +13365,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L123" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>11</v>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
@@ -13398,45 +13392,49 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W123" s="9" t="n">
-        <v>0</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W123" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X123" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC123" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC123" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13450,15 +13448,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1850126</v>
+        <v>3549525</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Lyon Toastmasters Unlimited</t>
+          <t>Lyon English Toastmasters</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13472,17 +13470,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L124" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -13499,7 +13497,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -13510,38 +13508,34 @@
       <c r="S124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T124" s="10" t="n">
-        <v>1</v>
+      <c r="T124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="10" t="n">
-        <v>1</v>
+      <c r="Z124" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC124" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13555,11 +13549,11 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>7064056</v>
+        <v>1850126</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Annecy</t>
+          <t>Lyon Toastmasters Unlimited</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
@@ -13577,13 +13571,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13604,7 +13598,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -13613,7 +13607,7 @@
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T125" s="10" t="n">
         <v>1</v>
@@ -13622,13 +13616,13 @@
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13640,11 +13634,11 @@
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC125" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -13660,15 +13654,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>28678901</v>
+        <v>7064056</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club Valence</t>
+          <t>Toastmasters Annecy</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13682,17 +13676,17 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L126" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M126" s="7" t="n">
@@ -13718,36 +13712,40 @@
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="9" t="n">
-        <v>2</v>
+      <c r="X126" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC126" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC126" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -13761,15 +13759,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>1530443</v>
+        <v>28678901</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Grand Lyon</t>
+          <t>Toastmasters Club Valence</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13783,17 +13781,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K127" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L127" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L127" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13810,10 +13808,10 @@
         </is>
       </c>
       <c r="P127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13821,8 +13819,8 @@
       <c r="S127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T127" s="10" t="n">
-        <v>1</v>
+      <c r="T127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
@@ -13833,26 +13831,22 @@
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="10" t="n">
-        <v>4</v>
+      <c r="X127" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="10" t="n">
-        <v>1</v>
+      <c r="Z127" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC127" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -13862,15 +13856,15 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>3657380</v>
+        <v>1530443</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Les Mots Passants</t>
+          <t>Toastmasters Grand Lyon</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
@@ -13888,10 +13882,10 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>0</v>
@@ -13918,7 +13912,7 @@
         <v>1</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13939,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13951,9 +13945,13 @@
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC128" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13967,15 +13965,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>2753458</v>
+        <v>3657380</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Aix En Provence - Le Cours Des Mots</t>
+          <t>Les Mots Passants</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13989,10 +13987,10 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K129" s="4" t="n">
         <v>0</v>
@@ -14016,7 +14014,7 @@
         </is>
       </c>
       <c r="P129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q129" s="9" t="n">
         <v>0</v>
@@ -14027,8 +14025,8 @@
       <c r="S129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T129" s="9" t="n">
-        <v>0</v>
+      <c r="T129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U129" s="9" t="n">
         <v>0</v>
@@ -14039,8 +14037,8 @@
       <c r="W129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X129" s="9" t="n">
-        <v>2</v>
+      <c r="X129" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -14052,7 +14050,7 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC129" s="4" t="inlineStr"/>
     </row>
@@ -14068,15 +14066,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>28678465</v>
+        <v>2753458</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Grand Avignon</t>
+          <t>Toastmasters Aix En Provence - Le Cours Des Mots</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14090,10 +14088,10 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0</v>
@@ -14120,7 +14118,7 @@
         <v>0</v>
       </c>
       <c r="Q130" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R130" s="9" t="n">
         <v>0</v>
@@ -14141,19 +14139,19 @@
         <v>0</v>
       </c>
       <c r="X130" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y130" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB130" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="Y130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB130" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="AC130" s="4" t="inlineStr"/>
     </row>
@@ -14169,15 +14167,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>4750231</v>
+        <v>28678465</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Marseille</t>
+          <t>Toastmasters Grand Avignon</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14191,13 +14189,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14218,10 +14216,10 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R131" s="9" t="n">
         <v>0</v>
@@ -14236,19 +14234,19 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="10" t="n">
-        <v>4</v>
+      <c r="X131" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="10" t="n">
-        <v>1</v>
+      <c r="Z131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14270,15 +14268,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>6666232</v>
+        <v>4750231</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Toulon</t>
+          <t>Toastmasters Marseille</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14292,17 +14290,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M132" s="7" t="n">
@@ -14319,7 +14317,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -14330,14 +14328,14 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
@@ -14355,7 +14353,7 @@
         <v>1</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC132" s="4" t="inlineStr"/>
     </row>
@@ -14367,19 +14365,19 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>7373921</v>
+        <v>6666232</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Eloquence Nice Toastmasters Club</t>
+          <t>Toastmasters Toulon</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14393,17 +14391,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L133" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
@@ -14438,31 +14436,27 @@
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y133" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB133" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB133" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC133" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14476,11 +14470,11 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>1387178</v>
+        <v>7373921</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Côte D'Azur</t>
+          <t>Eloquence Nice Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -14498,13 +14492,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
@@ -14543,13 +14537,13 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14581,15 +14575,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>2677777</v>
+        <v>1387178</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters NICE</t>
+          <t>Toastmasters Côte D'Azur</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14603,10 +14597,10 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K135" s="4" t="n">
         <v>0</v>
@@ -14659,8 +14653,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -14686,15 +14680,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>5038814</v>
+        <v>2677777</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Sophia Antipolis</t>
+          <t>Toastmasters NICE</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14708,10 +14702,10 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>0</v>
@@ -14746,8 +14740,8 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="10" t="n">
-        <v>1</v>
+      <c r="T136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
@@ -14759,28 +14753,133 @@
         <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB136" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC136" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="n">
+        <v>5038814</v>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>Toastmasters Sophia Antipolis</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F137" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G137" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J137" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K137" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M137" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O137" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y136" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA136" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB136" s="4" t="n">
+      <c r="Y137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC136" s="4" t="inlineStr">
+      <c r="AC137" s="4" t="inlineStr">
         <is>
           <t>Select Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC136"/>
+  <autoFilter ref="A1:AC137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14791,7 +14890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14900,7 +14999,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -14966,7 +15065,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15065,7 +15164,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15131,7 +15230,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15164,7 +15263,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15230,7 +15329,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15245,7 +15344,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -15296,7 +15395,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -15350,25 +15449,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -15377,7 +15476,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -15388,20 +15487,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -15410,7 +15509,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -15421,7 +15520,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -15443,7 +15542,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -15454,20 +15553,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>2.2</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -15476,25 +15575,25 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15509,7 +15608,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -15520,20 +15619,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -15542,7 +15641,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -15553,14 +15652,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15575,7 +15674,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -15586,20 +15685,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -15608,40 +15707,40 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
+        <v>3</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>4</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -15652,20 +15751,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -15674,7 +15773,7 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -15685,14 +15784,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15707,7 +15806,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -15718,20 +15817,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -15743,8 +15842,41 @@
         <v>4</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I28"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 37 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 17 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC137"/>
+  <dimension ref="A1:AC138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1163,7 +1163,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1233,8 +1233,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1649,8 +1649,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2154,8 +2154,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="P17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" s="9" t="n">
         <v>0</v>
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2574,8 +2574,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2974,10 +2974,10 @@
         <v>0</v>
       </c>
       <c r="S22" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U22" s="9" t="n">
         <v>0</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3099,8 +3099,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3410,8 +3410,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="10" t="n">
         <v>1</v>
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4339,8 +4339,8 @@
       <c r="Y35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z35" s="9" t="n">
-        <v>0</v>
+      <c r="Z35" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA35" s="10" t="n">
         <v>1</v>
@@ -4479,7 +4479,7 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4549,8 +4549,8 @@
       <c r="Y37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z37" s="9" t="n">
-        <v>0</v>
+      <c r="Z37" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA37" s="10" t="n">
         <v>1</v>
@@ -4992,11 +4992,11 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>28678531</v>
+        <v>28680209</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Mechelen Toastmasters</t>
+          <t>Lille English Toastmasters</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
@@ -5014,17 +5014,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="7" t="n">
@@ -5041,16 +5041,16 @@
         </is>
       </c>
       <c r="P42" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S42" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42" s="9" t="n">
         <v>0</v>
@@ -5064,8 +5064,8 @@
       <c r="W42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X42" s="10" t="n">
-        <v>5</v>
+      <c r="X42" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y42" s="9" t="n">
         <v>0</v>
@@ -5076,9 +5076,7 @@
       <c r="AA42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB42" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
@@ -5093,15 +5091,15 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1225462</v>
+        <v>28678531</v>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Antwerpen</t>
+          <t>Mechelen Toastmasters</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5115,13 +5113,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J43" s="4" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5142,28 +5140,28 @@
         </is>
       </c>
       <c r="P43" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q43" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T43" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="10" t="n">
-        <v>4</v>
+      <c r="V43" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>5</v>
@@ -5178,13 +5176,9 @@
         <v>1</v>
       </c>
       <c r="AB43" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5198,15 +5192,15 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>7242261</v>
+        <v>1225462</v>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Port of Antwerp</t>
+          <t>Toastmasters Antwerpen</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5220,13 +5214,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="J44" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5258,34 +5252,38 @@
       <c r="S44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T44" s="9" t="n">
-        <v>0</v>
+      <c r="T44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V44" s="9" t="n">
-        <v>0</v>
+      <c r="V44" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W44" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="X44" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z44" s="9" t="n">
-        <v>0</v>
+      <c r="Z44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA44" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB44" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5299,15 +5297,15 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>5739706</v>
+        <v>7242261</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>UPS Toastmasters Club</t>
+          <t>Toastmasters Port of Antwerp</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5321,17 +5319,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="J45" s="4" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="K45" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L45" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M45" s="7" t="n">
@@ -5351,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="Q45" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" s="9" t="n">
         <v>0</v>
@@ -5359,8 +5357,8 @@
       <c r="S45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T45" s="10" t="n">
-        <v>1</v>
+      <c r="T45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U45" s="9" t="n">
         <v>0</v>
@@ -5371,8 +5369,8 @@
       <c r="W45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X45" s="10" t="n">
-        <v>7</v>
+      <c r="X45" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y45" s="9" t="n">
         <v>0</v>
@@ -5384,7 +5382,7 @@
         <v>1</v>
       </c>
       <c r="AB45" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AC45" s="4" t="inlineStr"/>
     </row>
@@ -5396,19 +5394,19 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1363513</v>
+        <v>5739706</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Atomic Toastmasters</t>
+          <t>UPS Toastmasters Club</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5422,17 +5420,17 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M46" s="7" t="n">
@@ -5449,28 +5447,28 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="10" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W46" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="T46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X46" s="10" t="n">
         <v>7</v>
@@ -5485,13 +5483,9 @@
         <v>1</v>
       </c>
       <c r="AB46" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC46" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="AC46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5505,15 +5499,15 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>895375</v>
+        <v>1363513</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Claddagh Toastmasters</t>
+          <t>Atomic Toastmasters</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5527,17 +5521,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L47" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M47" s="7" t="n">
@@ -5556,14 +5550,14 @@
       <c r="P47" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q47" s="9" t="n">
-        <v>0</v>
+      <c r="Q47" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S47" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T47" s="9" t="n">
         <v>0</v>
@@ -5571,28 +5565,32 @@
       <c r="U47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W47" s="9" t="n">
-        <v>0</v>
+      <c r="V47" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W47" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X47" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB47" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5606,15 +5604,15 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>6046050</v>
+        <v>895375</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Dacia Toastmasters of Brussels</t>
+          <t>Claddagh Toastmasters</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5628,17 +5626,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K48" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L48" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="7" t="n">
@@ -5655,7 +5653,7 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
         <v>0</v>
@@ -5666,8 +5664,8 @@
       <c r="S48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="10" t="n">
-        <v>1</v>
+      <c r="T48" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U48" s="9" t="n">
         <v>0</v>
@@ -5679,25 +5677,21 @@
         <v>0</v>
       </c>
       <c r="X48" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="10" t="n">
-        <v>1</v>
+      <c r="Z48" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB48" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC48" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5711,11 +5705,11 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>28679872</v>
+        <v>6046050</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>De Sprekersclub Brussel</t>
+          <t>Dacia Toastmasters of Brussels</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -5733,13 +5727,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
@@ -5778,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5796,7 +5790,7 @@
         <v>1</v>
       </c>
       <c r="AB49" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC49" s="4" t="inlineStr">
         <is>
@@ -5816,15 +5810,15 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>5916770</v>
+        <v>28679872</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>SpeakClear EuroClear Corporate TM</t>
+          <t>De Sprekersclub Brussel</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5838,13 +5832,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5865,31 +5859,31 @@
         </is>
       </c>
       <c r="P50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U50" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V50" s="10" t="n">
-        <v>4</v>
+      <c r="U50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X50" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5901,11 +5895,11 @@
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AC50" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -5921,15 +5915,15 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>7970940</v>
+        <v>5916770</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Talking Tigers</t>
+          <t>SpeakClear EuroClear Corporate TM</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5943,17 +5937,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
@@ -5970,31 +5964,31 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="V51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="X51" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -6006,31 +6000,35 @@
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>28676717</v>
+        <v>7970940</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Amazon Netherlands Toastmasters Club</t>
+          <t>Talking Tigers</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6044,10 +6042,10 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>0</v>
@@ -6095,13 +6093,13 @@
         <v>0</v>
       </c>
       <c r="X52" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -6123,15 +6121,15 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>28678598</v>
+        <v>28676717</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Amstelveen Toastmasters</t>
+          <t>Amazon Netherlands Toastmasters Club</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6145,17 +6143,17 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="K53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L53" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M53" s="7" t="n">
@@ -6172,49 +6170,45 @@
         </is>
       </c>
       <c r="P53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="10" t="n">
-        <v>1</v>
+      <c r="Z53" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC53" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -6228,15 +6222,15 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>4943729</v>
+        <v>28678598</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Amsterdam Early Bird Toastmasters</t>
+          <t>Amstelveen Toastmasters</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6250,10 +6244,10 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="K54" s="4" t="n">
         <v>0</v>
@@ -6277,22 +6271,22 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q54" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T54" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" s="10" t="n">
-        <v>1</v>
+      <c r="T54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
         <v>0</v>
@@ -6301,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="X54" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
@@ -6333,11 +6327,11 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>9210</v>
+        <v>4943729</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Amsterdam Toastmasters Club</t>
+          <t>Amsterdam Early Bird Toastmasters</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -6381,14 +6375,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P55" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q55" s="9" t="n">
-        <v>0</v>
+      <c r="P55" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q55" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S55" s="9" t="n">
         <v>0</v>
@@ -6438,15 +6432,15 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>3074183</v>
+        <v>9210</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Fusion Toastmasters Amsterdam</t>
+          <t>Amsterdam Toastmasters Club</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6460,10 +6454,10 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K56" s="4" t="n">
         <v>0</v>
@@ -6486,8 +6480,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P56" s="9" t="n">
-        <v>0</v>
+      <c r="P56" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6498,11 +6492,11 @@
       <c r="S56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="9" t="n">
-        <v>0</v>
+      <c r="T56" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V56" s="9" t="n">
         <v>0</v>
@@ -6511,7 +6505,7 @@
         <v>0</v>
       </c>
       <c r="X56" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6523,11 +6517,11 @@
         <v>1</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC56" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -6539,19 +6533,19 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>5991893</v>
+        <v>3074183</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Amsterdamse Brugman Club</t>
+          <t>Fusion Toastmasters Amsterdam</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6565,10 +6559,10 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="K57" s="4" t="n">
         <v>0</v>
@@ -6592,7 +6586,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -6603,8 +6597,8 @@
       <c r="S57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="10" t="n">
-        <v>1</v>
+      <c r="T57" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U57" s="9" t="n">
         <v>0</v>
@@ -6615,8 +6609,8 @@
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="9" t="n">
-        <v>0</v>
+      <c r="X57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6628,9 +6622,13 @@
         <v>1</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC57" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -6644,15 +6642,15 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>587070</v>
+        <v>5991893</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>De Sprekers Club</t>
+          <t>Amsterdamse Brugman Club</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6666,17 +6664,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M58" s="7" t="n">
@@ -6693,7 +6691,7 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>0</v>
@@ -6704,26 +6702,26 @@
       <c r="S58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X58" s="10" t="n">
-        <v>6</v>
+      <c r="X58" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -6745,15 +6743,15 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>28678697</v>
+        <v>587070</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Fluor Toastmasters</t>
+          <t>De Sprekers Club</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6770,10 +6768,10 @@
         <v>15</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="8" t="inlineStr">
         <is>
@@ -6812,25 +6810,25 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X59" s="9" t="n">
-        <v>0</v>
+      <c r="X59" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC59" s="4" t="inlineStr"/>
     </row>
@@ -6846,15 +6844,15 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>803664</v>
+        <v>28678697</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Het Sprekersgilde</t>
+          <t>Fluor Toastmasters</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6868,17 +6866,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="7" t="n">
@@ -6913,31 +6911,27 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X60" s="10" t="n">
-        <v>4</v>
+      <c r="X60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="10" t="n">
-        <v>1</v>
+      <c r="Z60" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC60" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6951,15 +6945,15 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>3376324</v>
+        <v>803664</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters STCA</t>
+          <t>Het Sprekersgilde</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6973,25 +6967,25 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M61" s="7" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O61" s="8" t="inlineStr">
@@ -7018,27 +7012,31 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X61" s="9" t="n">
-        <v>0</v>
+      <c r="X61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7048,19 +7046,19 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>5757882</v>
+        <v>3376324</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Domstad Toastmasters</t>
+          <t>Toastmasters STCA</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7074,25 +7072,25 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O62" s="8" t="inlineStr">
@@ -7119,25 +7117,25 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X62" s="10" t="n">
-        <v>5</v>
+      <c r="X62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="10" t="n">
-        <v>1</v>
+      <c r="Z62" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC62" s="4" t="inlineStr"/>
     </row>
@@ -7153,15 +7151,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>711294</v>
+        <v>5757882</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Taste and Toastmasters Club</t>
+          <t>Domstad Toastmasters</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7175,13 +7173,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7202,7 +7200,7 @@
         </is>
       </c>
       <c r="P63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
         <v>0</v>
@@ -7213,38 +7211,34 @@
       <c r="S63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T63" s="9" t="n">
-        <v>0</v>
+      <c r="T63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y63" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB63" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="W63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z63" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA63" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB63" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC63" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7258,15 +7252,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>3177173</v>
+        <v>711294</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>U-Speak!</t>
+          <t>Taste and Toastmasters Club</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7280,13 +7274,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
@@ -7318,36 +7312,36 @@
       <c r="S64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T64" s="10" t="n">
-        <v>1</v>
+      <c r="T64" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X64" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y64" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA64" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB64" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y64" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA64" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB64" s="4" t="n">
-        <v>10</v>
-      </c>
       <c r="AC64" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -7363,15 +7357,15 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>849157</v>
+        <v>3177173</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Utrecht Toastmasters Club</t>
+          <t>U-Speak!</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7385,13 +7379,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
@@ -7412,7 +7406,7 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="9" t="n">
         <v>0</v>
@@ -7421,22 +7415,22 @@
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U65" s="10" t="n">
-        <v>1</v>
+      <c r="U65" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
@@ -7464,19 +7458,19 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1861273</v>
+        <v>849157</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Amersfoort Toastmasters Club</t>
+          <t>Utrecht Toastmasters Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7493,10 +7487,10 @@
         <v>40</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
@@ -7520,28 +7514,28 @@
         <v>0</v>
       </c>
       <c r="Q66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S66" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" s="9" t="n">
-        <v>0</v>
+      <c r="S66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7553,11 +7547,11 @@
         <v>1</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -7573,15 +7567,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>3559370</v>
+        <v>1861273</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Gouden Raad Toastmasters</t>
+          <t>Amersfoort Toastmasters Club</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7595,17 +7589,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L67" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M67" s="7" t="n">
@@ -7625,13 +7619,13 @@
         <v>0</v>
       </c>
       <c r="Q67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="9" t="n">
-        <v>0</v>
+      <c r="S67" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T67" s="9" t="n">
         <v>0</v>
@@ -7640,27 +7634,31 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X67" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y67" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB67" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA67" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB67" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC67" s="4" t="inlineStr"/>
+      <c r="AC67" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -7674,15 +7672,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>28679949</v>
+        <v>3559370</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Mainfreight Toastmasters</t>
+          <t>Gouden Raad Toastmasters</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7696,17 +7694,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="7" t="n">
@@ -7741,24 +7739,26 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X68" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB68" s="4" t="n"/>
+      <c r="AB68" s="4" t="n">
+        <v>3</v>
+      </c>
       <c r="AC68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
@@ -7773,15 +7773,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>3168775</v>
+        <v>28679949</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>NOA Toastmasters Club</t>
+          <t>Mainfreight Toastmasters</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7795,13 +7795,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7833,14 +7833,14 @@
       <c r="S69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T69" s="10" t="n">
-        <v>1</v>
+      <c r="T69" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U69" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7851,20 +7851,14 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="10" t="n">
-        <v>1</v>
+      <c r="Z69" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB69" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC69" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AB69" s="4" t="n"/>
+      <c r="AC69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7878,15 +7872,15 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>5011652</v>
+        <v>3168775</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Wageningen</t>
+          <t>NOA Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7900,13 +7894,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J70" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="J70" s="4" t="n">
-        <v>19</v>
-      </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7938,20 +7932,20 @@
       <c r="S70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X70" s="9" t="n">
-        <v>2</v>
+      <c r="X70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7963,9 +7957,13 @@
         <v>1</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC70" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7975,19 +7973,19 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>3323798</v>
+        <v>5011652</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Apeldoorn Toastmasters</t>
+          <t>Toastmasters Wageningen</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -8001,13 +7999,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8036,41 +8034,37 @@
       <c r="R71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="10" t="n">
+      <c r="S71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="T71" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U71" s="10" t="n">
+      <c r="Y71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB71" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="V71" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X71" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z71" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA71" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB71" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC71" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AC71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -8084,15 +8078,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>5062025</v>
+        <v>3323798</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Deventer Toastmasters</t>
+          <t>Apeldoorn Toastmasters</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8106,13 +8100,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8133,25 +8127,25 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" s="9" t="n">
-        <v>0</v>
+      <c r="S72" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="V72" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
@@ -8169,11 +8163,11 @@
         <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -8189,11 +8183,11 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>28678587</v>
+        <v>5062025</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>English Deventer Toastmasters Club</t>
+          <t>Deventer Toastmasters</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
@@ -8211,10 +8205,10 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K73" s="4" t="n">
         <v>0</v>
@@ -8238,16 +8232,16 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="10" t="n">
         <v>1</v>
@@ -8274,11 +8268,11 @@
         <v>1</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AC73" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -8294,15 +8288,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1838841</v>
+        <v>28678587</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Twente Toastmasters</t>
+          <t>English Deventer Toastmasters Club</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8346,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="Q74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" s="9" t="n">
         <v>0</v>
@@ -8354,8 +8348,8 @@
       <c r="S74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T74" s="9" t="n">
-        <v>0</v>
+      <c r="T74" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U74" s="9" t="n">
         <v>0</v>
@@ -8367,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="X74" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8379,11 +8373,11 @@
         <v>1</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC74" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -8399,15 +8393,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>28678604</v>
+        <v>1838841</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Vliegende Hollanders ONLINE Advanced Toastmasters</t>
+          <t>Twente Toastmasters</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8421,13 +8415,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J75" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="J75" s="4" t="n">
-        <v>19</v>
-      </c>
       <c r="K75" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
@@ -8451,7 +8445,7 @@
         <v>0</v>
       </c>
       <c r="Q75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8465,14 +8459,14 @@
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="10" t="n">
-        <v>4</v>
+      <c r="V75" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W75" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8484,9 +8478,13 @@
         <v>1</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC75" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8496,19 +8494,19 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2997331</v>
+        <v>28678604</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Almere Toastmasters</t>
+          <t>Vliegende Hollanders ONLINE Advanced Toastmasters</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8522,17 +8520,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="J76" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="J76" s="4" t="n">
-        <v>18</v>
-      </c>
       <c r="K76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M76" s="7" t="n">
@@ -8552,7 +8550,7 @@
         <v>0</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8566,14 +8564,14 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>1</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8585,13 +8583,9 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC76" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8605,15 +8599,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>801134</v>
+        <v>2997331</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>SpreekMeesters</t>
+          <t>Almere Toastmasters</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8627,17 +8621,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="7" t="n">
@@ -8654,16 +8648,16 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="10" t="n">
-        <v>2</v>
+      <c r="S77" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T77" s="9" t="n">
         <v>0</v>
@@ -8671,14 +8665,14 @@
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V77" s="10" t="n">
-        <v>4</v>
+      <c r="V77" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X77" s="9" t="n">
-        <v>1</v>
+      <c r="X77" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8710,15 +8704,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>4221558</v>
+        <v>801134</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Groningen</t>
+          <t>SpreekMeesters</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8732,13 +8726,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
@@ -8759,7 +8753,7 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="9" t="n">
         <v>0</v>
@@ -8767,8 +8761,8 @@
       <c r="R78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S78" s="9" t="n">
-        <v>0</v>
+      <c r="S78" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T78" s="9" t="n">
         <v>0</v>
@@ -8776,14 +8770,14 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>2</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="10" t="n">
-        <v>5</v>
+      <c r="X78" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
@@ -8795,11 +8789,11 @@
         <v>1</v>
       </c>
       <c r="AB78" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC78" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -8815,11 +8809,11 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>28677726</v>
+        <v>4221558</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters NOP</t>
+          <t>Toastmasters Groningen</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -8837,13 +8831,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
@@ -8867,7 +8861,7 @@
         <v>0</v>
       </c>
       <c r="Q79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" s="9" t="n">
         <v>0</v>
@@ -8882,13 +8876,13 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="9" t="n">
-        <v>3</v>
+      <c r="X79" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
@@ -8900,11 +8894,11 @@
         <v>1</v>
       </c>
       <c r="AB79" s="4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC79" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -8916,19 +8910,19 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>0A</t>
+          <t>06</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>28680117</v>
+        <v>28677726</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Impact Toastmasters</t>
+          <t>Toastmasters NOP</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8942,10 +8936,10 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K80" s="4" t="n">
         <v>0</v>
@@ -8972,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8993,41 +8987,47 @@
         <v>0</v>
       </c>
       <c r="X80" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z80" s="9" t="n">
-        <v>0</v>
+      <c r="Z80" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA80" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB80" s="4" t="n"/>
-      <c r="AC80" s="4" t="inlineStr"/>
+      <c r="AB80" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0A</t>
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>2175</v>
+        <v>28680117</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Bossuet Gaveliers Toastmasters Club</t>
+          <t>Impact Toastmasters</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -9041,13 +9041,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
@@ -9086,31 +9086,25 @@
         <v>0</v>
       </c>
       <c r="V81" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X81" s="10" t="n">
-        <v>4</v>
+      <c r="X81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="10" t="n">
-        <v>1</v>
+      <c r="Z81" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB81" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC81" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB81" s="4" t="n"/>
+      <c r="AC81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -9124,11 +9118,11 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>491</v>
+        <v>2175</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Green Heart Club</t>
+          <t>Bossuet Gaveliers Toastmasters Club</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
@@ -9146,10 +9140,10 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J82" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K82" s="4" t="n">
         <v>1</v>
@@ -9182,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" s="9" t="n">
         <v>0</v>
@@ -9209,11 +9203,11 @@
         <v>1</v>
       </c>
       <c r="AB82" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC82" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -9229,11 +9223,11 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>5429561</v>
+        <v>491</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Have Your Say</t>
+          <t>Green Heart Club</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -9251,17 +9245,17 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K83" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L83" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M83" s="7" t="n">
@@ -9287,7 +9281,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T83" s="9" t="n">
         <v>0</v>
@@ -9301,8 +9295,8 @@
       <c r="W83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X83" s="9" t="n">
-        <v>3</v>
+      <c r="X83" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -9314,9 +9308,13 @@
         <v>1</v>
       </c>
       <c r="AB83" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC83" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC83" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -9330,15 +9328,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>921076</v>
+        <v>5429561</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Sprich to Me</t>
+          <t>Have Your Say</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9352,13 +9350,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="8" t="inlineStr">
         <is>
@@ -9397,25 +9395,25 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X84" s="10" t="n">
-        <v>6</v>
+      <c r="X84" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB84" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC84" s="4" t="inlineStr"/>
     </row>
@@ -9431,15 +9429,15 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>4145151</v>
+        <v>921076</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>State Street Tales</t>
+          <t>Sprich to Me</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9453,17 +9451,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K85" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L85" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="7" t="n">
@@ -9503,14 +9501,14 @@
       <c r="W85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X85" s="9" t="n">
-        <v>3</v>
+      <c r="X85" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="10" t="n">
-        <v>1</v>
+      <c r="Z85" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9528,15 +9526,15 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>7709093</v>
+        <v>4145151</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Club Des Orateurs De Strasbourg</t>
+          <t>State Street Tales</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
@@ -9554,10 +9552,10 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
         <v>0</v>
@@ -9605,7 +9603,7 @@
         <v>0</v>
       </c>
       <c r="X86" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
@@ -9617,7 +9615,7 @@
         <v>1</v>
       </c>
       <c r="AB86" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC86" s="4" t="inlineStr"/>
     </row>
@@ -9633,11 +9631,11 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>7067</v>
+        <v>7709093</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Les Orateurs De Luxembourg</t>
+          <t>Club Des Orateurs De Strasbourg</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
@@ -9655,17 +9653,17 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J87" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L87" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M87" s="7" t="n">
@@ -9700,13 +9698,13 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="10" t="n">
-        <v>5</v>
+      <c r="X87" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
@@ -9718,7 +9716,7 @@
         <v>1</v>
       </c>
       <c r="AB87" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AC87" s="4" t="inlineStr"/>
     </row>
@@ -9734,15 +9732,15 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>5032586</v>
+        <v>7067</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Les Orateurs de Thionville</t>
+          <t>Les Orateurs De Luxembourg</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9756,13 +9754,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="8" t="inlineStr">
         <is>
@@ -9801,25 +9799,25 @@
         <v>0</v>
       </c>
       <c r="V88" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X88" s="9" t="n">
-        <v>0</v>
+      <c r="X88" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="9" t="n">
-        <v>0</v>
+      <c r="Z88" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA88" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB88" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC88" s="4" t="inlineStr"/>
     </row>
@@ -9835,11 +9833,11 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>834396</v>
+        <v>5032586</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Metzmerising Toastmasters Club</t>
+          <t>Les Orateurs de Thionville</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -9857,10 +9855,10 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K89" s="4" t="n">
         <v>0</v>
@@ -9908,7 +9906,7 @@
         <v>0</v>
       </c>
       <c r="X89" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9932,15 +9930,15 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>28675493</v>
+        <v>834396</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>BIL Public Speakers</t>
+          <t>Metzmerising Toastmasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
@@ -9958,10 +9956,10 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K90" s="4" t="n">
         <v>0</v>
@@ -10008,8 +10006,8 @@
       <c r="W90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X90" s="9" t="n">
-        <v>1</v>
+      <c r="X90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -10021,7 +10019,7 @@
         <v>1</v>
       </c>
       <c r="AB90" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC90" s="4" t="inlineStr"/>
     </row>
@@ -10037,11 +10035,11 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>858404</v>
+        <v>28675493</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Casemates Communicators Luxembourg</t>
+          <t>BIL Public Speakers</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -10059,10 +10057,10 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K91" s="4" t="n">
         <v>0</v>
@@ -10095,7 +10093,7 @@
         <v>0</v>
       </c>
       <c r="S91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T91" s="9" t="n">
         <v>0</v>
@@ -10109,8 +10107,8 @@
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="10" t="n">
-        <v>5</v>
+      <c r="X91" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
@@ -10122,7 +10120,7 @@
         <v>1</v>
       </c>
       <c r="AB91" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC91" s="4" t="inlineStr"/>
     </row>
@@ -10138,11 +10136,11 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>2187867</v>
+        <v>858404</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>EIB Toastmasters Club</t>
+          <t>Casemates Communicators Luxembourg</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
@@ -10160,17 +10158,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L92" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="7" t="n">
@@ -10196,7 +10194,7 @@
         <v>0</v>
       </c>
       <c r="S92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T92" s="9" t="n">
         <v>0</v>
@@ -10205,13 +10203,13 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
@@ -10223,13 +10221,9 @@
         <v>1</v>
       </c>
       <c r="AB92" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC92" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -10243,11 +10237,11 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>7208895</v>
+        <v>2187867</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Pitch Craft For Entrepreneurs Toastmasters</t>
+          <t>EIB Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -10265,13 +10259,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
@@ -10301,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="S93" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T93" s="9" t="n">
         <v>0</v>
@@ -10310,29 +10304,29 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y93" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB93" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Y93" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA93" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB93" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="AC93" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -10344,19 +10338,19 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>6286</v>
+        <v>7208895</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Agora 75 Club</t>
+          <t>Pitch Craft For Entrepreneurs Toastmasters</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10370,13 +10364,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
@@ -10399,8 +10393,8 @@
       <c r="P94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q94" s="10" t="n">
-        <v>2</v>
+      <c r="Q94" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R94" s="9" t="n">
         <v>0</v>
@@ -10408,20 +10402,20 @@
       <c r="S94" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T94" s="10" t="n">
-        <v>1</v>
+      <c r="T94" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X94" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -10433,11 +10427,11 @@
         <v>1</v>
       </c>
       <c r="AB94" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC94" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -10453,15 +10447,15 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>7955657</v>
+        <v>6286</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Ateme Toastmasters</t>
+          <t>Agora 75 Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10475,17 +10469,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M95" s="7" t="n">
@@ -10504,23 +10498,23 @@
       <c r="P95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" s="9" t="n">
-        <v>0</v>
+      <c r="Q95" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U95" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -10537,8 +10531,14 @@
       <c r="AA95" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB95" s="4" t="n"/>
-      <c r="AC95" s="4" t="inlineStr"/>
+      <c r="AB95" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -10552,15 +10552,15 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>6631</v>
+        <v>7955657</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Forum des Rives de Seine</t>
+          <t>Ateme Toastmasters</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10574,17 +10574,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="J96" s="4" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L96" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="7" t="n">
@@ -10618,15 +10618,15 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="10" t="n">
+      <c r="V96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W96" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X96" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X96" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
@@ -10636,9 +10636,7 @@
       <c r="AA96" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB96" s="4" t="n">
-        <v>4</v>
-      </c>
+      <c r="AB96" s="4" t="n"/>
       <c r="AC96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
@@ -10653,15 +10651,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1575</v>
+        <v>6631</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters 75</t>
+          <t>Forum des Rives de Seine</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10675,13 +10673,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
@@ -10702,7 +10700,7 @@
         </is>
       </c>
       <c r="P97" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q97" s="9" t="n">
         <v>0</v>
@@ -10713,20 +10711,20 @@
       <c r="S97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U97" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
+      <c r="T97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X97" s="9" t="n">
-        <v>3</v>
+      <c r="X97" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
@@ -10738,13 +10736,9 @@
         <v>1</v>
       </c>
       <c r="AB97" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC97" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -10758,15 +10752,15 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>7776982</v>
+        <v>1575</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Polyglottes Paris</t>
+          <t>Toastmasters 75</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10780,13 +10774,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
@@ -10807,7 +10801,7 @@
         </is>
       </c>
       <c r="P98" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" s="9" t="n">
         <v>0</v>
@@ -10818,20 +10812,20 @@
       <c r="S98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V98" s="10" t="n">
-        <v>4</v>
+      <c r="T98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U98" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V98" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="10" t="n">
-        <v>4</v>
+      <c r="X98" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10854,24 +10848,24 @@
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>7308562</v>
+        <v>7776982</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Den Haag Toastmasters</t>
+          <t>Toastmasters Polyglottes Paris</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F99" s="6" t="n">
         <v>10</v>
@@ -10885,13 +10879,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
@@ -10929,28 +10923,32 @@
       <c r="U99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V99" s="9" t="n">
-        <v>1</v>
+      <c r="V99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W99" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X99" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="X99" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z99" s="9" t="n">
-        <v>0</v>
+      <c r="Z99" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA99" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB99" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC99" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -10964,11 +10962,11 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1523749</v>
+        <v>7308562</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>International Toastmasters The Hague</t>
+          <t>Den Haag Toastmasters</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
@@ -10986,17 +10984,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M100" s="7" t="n">
@@ -11022,34 +11020,34 @@
         <v>0</v>
       </c>
       <c r="S100" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T100" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X100" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="9" t="n">
-        <v>0</v>
+      <c r="Z100" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB100" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC100" s="4" t="inlineStr"/>
     </row>
@@ -11065,15 +11063,15 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1550131</v>
+        <v>1523749</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Leiden Toastmasters</t>
+          <t>International Toastmasters The Hague</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11087,17 +11085,17 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L101" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L101" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M101" s="7" t="n">
@@ -11114,7 +11112,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -11123,22 +11121,22 @@
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U101" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V101" s="10" t="n">
-        <v>4</v>
+      <c r="U101" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X101" s="10" t="n">
-        <v>6</v>
+      <c r="X101" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y101" s="9" t="n">
         <v>0</v>
@@ -11150,13 +11148,9 @@
         <v>1</v>
       </c>
       <c r="AB101" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC101" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11170,15 +11164,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>5501964</v>
+        <v>1550131</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>The Hague University Toastmasters</t>
+          <t>Leiden Toastmasters</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11192,17 +11186,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L102" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M102" s="7" t="n">
@@ -11219,7 +11213,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -11230,20 +11224,20 @@
       <c r="S102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="9" t="n">
-        <v>2</v>
+      <c r="T102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U102" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V102" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X102" s="9" t="n">
-        <v>2</v>
+      <c r="X102" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -11255,11 +11249,11 @@
         <v>1</v>
       </c>
       <c r="AB102" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC102" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -11275,11 +11269,11 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>620921</v>
+        <v>5501964</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of The Hague</t>
+          <t>The Hague University Toastmasters</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
@@ -11297,17 +11291,17 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L103" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L103" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M103" s="7" t="n">
@@ -11324,31 +11318,31 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V103" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="10" t="n">
-        <v>6</v>
+      <c r="X103" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
@@ -11360,11 +11354,11 @@
         <v>1</v>
       </c>
       <c r="AB103" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC103" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -11376,19 +11370,19 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>28678723</v>
+        <v>620921</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>CC7 Europe Toastmasters</t>
+          <t>Toastmasters of The Hague</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11402,17 +11396,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="J104" s="4" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L104" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M104" s="7" t="n">
@@ -11429,7 +11423,7 @@
         </is>
       </c>
       <c r="P104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q104" s="9" t="n">
         <v>0</v>
@@ -11452,22 +11446,26 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="9" t="n">
-        <v>3</v>
+      <c r="X104" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC104" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -11481,15 +11479,15 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>3697073</v>
+        <v>28678723</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>McDermott TM The Hague</t>
+          <t>CC7 Europe Toastmasters</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11503,13 +11501,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L105" s="8" t="inlineStr">
         <is>
@@ -11530,7 +11528,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11548,25 +11546,25 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="10" t="n">
-        <v>4</v>
+      <c r="X105" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z105" s="10" t="n">
-        <v>1</v>
+      <c r="Z105" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA105" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB105" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC105" s="4" t="inlineStr"/>
     </row>
@@ -11582,35 +11580,35 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>7632518</v>
+        <v>3697073</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Shell Toastmasters Club Rotterdam</t>
+          <t>McDermott TM The Hague</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="K106" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F106" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G106" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H106" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I106" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="J106" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="K106" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L106" s="8" t="inlineStr">
         <is>
@@ -11631,10 +11629,10 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R106" s="9" t="n">
         <v>0</v>
@@ -11642,32 +11640,32 @@
       <c r="S106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T106" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U106" s="10" t="n">
-        <v>1</v>
+      <c r="T106" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V106" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="9" t="n">
-        <v>2</v>
+      <c r="X106" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB106" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC106" s="4" t="inlineStr"/>
     </row>
@@ -11683,15 +11681,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>3943870</v>
+        <v>7632518</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Shell Toastmasters The Hague Club</t>
+          <t>Shell Toastmasters Club Rotterdam</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11708,10 +11706,10 @@
         <v>11</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="8" t="inlineStr">
         <is>
@@ -11735,7 +11733,7 @@
         <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R107" s="9" t="n">
         <v>0</v>
@@ -11743,32 +11741,32 @@
       <c r="S107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T107" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" s="9" t="n">
-        <v>0</v>
+      <c r="T107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U107" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X107" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z107" s="10" t="n">
-        <v>1</v>
+      <c r="Z107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA107" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB107" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC107" s="4" t="inlineStr"/>
     </row>
@@ -11784,15 +11782,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>28677998</v>
+        <v>3943870</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Swift Toastmasters</t>
+          <t>Shell Toastmasters The Hague Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11806,17 +11804,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L108" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M108" s="7" t="n">
@@ -11833,49 +11831,45 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB108" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="R108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA108" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB108" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC108" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -11889,15 +11883,15 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>28677500</v>
+        <v>28677998</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Worley WeME Toastmaster</t>
+          <t>Swift Toastmasters</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11911,17 +11905,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L109" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M109" s="7" t="n">
@@ -11938,10 +11932,10 @@
         </is>
       </c>
       <c r="P109" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q109" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R109" s="9" t="n">
         <v>0</v>
@@ -11956,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11968,15 +11962,19 @@
         <v>0</v>
       </c>
       <c r="Z109" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB109" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -11986,19 +11984,19 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>7274025</v>
+        <v>28677500</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Den Bosch Toastmasters Club</t>
+          <t>Worley WeME Toastmaster</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -12012,17 +12010,17 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="J110" s="4" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="K110" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="L110" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L110" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M110" s="7" t="n">
@@ -12039,10 +12037,10 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R110" s="9" t="n">
         <v>0</v>
@@ -12050,8 +12048,8 @@
       <c r="S110" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T110" s="10" t="n">
-        <v>1</v>
+      <c r="T110" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
@@ -12062,8 +12060,8 @@
       <c r="W110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X110" s="10" t="n">
-        <v>4</v>
+      <c r="X110" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y110" s="9" t="n">
         <v>0</v>
@@ -12075,13 +12073,9 @@
         <v>1</v>
       </c>
       <c r="AB110" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC110" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12095,15 +12089,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>935413</v>
+        <v>7274025</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Rotterdam Toastmasters</t>
+          <t>Den Bosch Toastmasters Club</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12117,13 +12111,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
@@ -12144,10 +12138,10 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" s="9" t="n">
         <v>0</v>
@@ -12155,21 +12149,21 @@
       <c r="S111" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T111" s="9" t="n">
-        <v>0</v>
+      <c r="T111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="10" t="n">
+      <c r="V111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W111" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W111" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="X111" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
@@ -12180,11 +12174,11 @@
         <v>1</v>
       </c>
       <c r="AB111" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC111" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12200,15 +12194,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>28679394</v>
+        <v>935413</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>RSM Toastmasters Club</t>
+          <t>Rotterdam Toastmasters</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12222,13 +12216,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
@@ -12258,7 +12252,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -12266,28 +12260,32 @@
       <c r="U112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" s="9" t="n">
-        <v>0</v>
+      <c r="V112" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W112" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X112" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="9" t="n">
-        <v>0</v>
+      <c r="Z112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB112" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC112" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC112" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -12301,15 +12299,15 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1994030</v>
+        <v>28679394</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Sprekershaven Toastmasters Rotterdam</t>
+          <t>RSM Toastmasters Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -12323,13 +12321,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12368,31 +12366,27 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="10" t="n">
-        <v>5</v>
+      <c r="X113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z113" s="10" t="n">
-        <v>1</v>
+      <c r="Z113" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA113" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB113" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC113" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12406,11 +12400,11 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>28678590</v>
+        <v>1994030</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Breda</t>
+          <t>Sprekershaven Toastmasters Rotterdam</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -12428,13 +12422,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="J114" s="4" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
@@ -12455,10 +12449,10 @@
         </is>
       </c>
       <c r="P114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" s="9" t="n">
         <v>0</v>
@@ -12473,13 +12467,13 @@
         <v>0</v>
       </c>
       <c r="V114" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X114" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
@@ -12511,11 +12505,11 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>4386342</v>
+        <v>28678590</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Tilburg</t>
+          <t>Toastmasters Breda</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
@@ -12533,13 +12527,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12578,13 +12572,13 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X115" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
@@ -12596,11 +12590,11 @@
         <v>1</v>
       </c>
       <c r="AB115" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AC115" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12612,15 +12606,15 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>7930894</v>
+        <v>4386342</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>ASML Toastmasters</t>
+          <t>Toastmasters Tilburg</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
@@ -12638,13 +12632,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12665,7 +12659,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>1</v>
@@ -12676,36 +12670,36 @@
       <c r="S116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="10" t="n">
-        <v>1</v>
+      <c r="T116" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X116" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA116" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB116" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC116" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Select Distinguished</t>
         </is>
       </c>
     </row>
@@ -12721,15 +12715,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1071665</v>
+        <v>7930894</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Lighttown Speakers</t>
+          <t>ASML Toastmasters</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12743,13 +12737,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12778,8 +12772,8 @@
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="10" t="n">
-        <v>2</v>
+      <c r="S117" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="T117" s="10" t="n">
         <v>1</v>
@@ -12787,15 +12781,15 @@
       <c r="U117" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V117" s="10" t="n">
+      <c r="V117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W117" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X117" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
@@ -12806,11 +12800,11 @@
         <v>1</v>
       </c>
       <c r="AB117" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC117" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -12826,15 +12820,15 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>777407</v>
+        <v>1071665</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Eindhoven</t>
+          <t>Lighttown Speakers</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F118" s="6" t="n">
         <v>10</v>
@@ -12848,13 +12842,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12875,31 +12869,31 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q118" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S118" s="9" t="n">
-        <v>0</v>
+      <c r="S118" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U118" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V118" s="9" t="n">
-        <v>2</v>
+      <c r="U118" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V118" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X118" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12911,11 +12905,11 @@
         <v>1</v>
       </c>
       <c r="AB118" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC118" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -12931,15 +12925,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1933731</v>
+        <v>777407</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Maastricht</t>
+          <t>Toastmasters Eindhoven</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12953,13 +12947,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
@@ -12980,7 +12974,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q119" s="9" t="n">
         <v>0</v>
@@ -12989,22 +12983,22 @@
         <v>0</v>
       </c>
       <c r="S119" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T119" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X119" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -13027,24 +13021,24 @@
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>28677576</v>
+        <v>1933731</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Dell France Toastmasters</t>
+          <t>Toastmasters Maastricht</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13058,17 +13052,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L120" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M120" s="7" t="n">
@@ -13094,7 +13088,7 @@
         <v>0</v>
       </c>
       <c r="S120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T120" s="9" t="n">
         <v>0</v>
@@ -13108,22 +13102,26 @@
       <c r="W120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X120" s="9" t="n">
-        <v>2</v>
+      <c r="X120" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB120" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC120" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC120" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -13137,11 +13135,11 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>28678280</v>
+        <v>28677576</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Bordeaux</t>
+          <t>Dell France Toastmasters</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
@@ -13159,17 +13157,17 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L121" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L121" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M121" s="7" t="n">
@@ -13186,32 +13184,32 @@
         </is>
       </c>
       <c r="P121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W121" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X121" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W121" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X121" s="10" t="n">
-        <v>7</v>
-      </c>
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
@@ -13222,13 +13220,9 @@
         <v>1</v>
       </c>
       <c r="AB121" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC121" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -13242,39 +13236,39 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>3365085</v>
+        <v>28678280</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Toulouse Speakers</t>
+          <t>Toastmasters Bordeaux</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="J122" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="K122" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F122" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G122" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H122" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I122" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="J122" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K122" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L122" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M122" s="7" t="n">
@@ -13291,10 +13285,10 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R122" s="9" t="n">
         <v>0</v>
@@ -13302,14 +13296,14 @@
       <c r="S122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T122" s="10" t="n">
-        <v>1</v>
+      <c r="T122" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U122" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13329,7 +13323,11 @@
       <c r="AB122" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -13343,15 +13341,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1095816</v>
+        <v>3365085</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Toulouse Toastmasters Communication</t>
+          <t>Toulouse Speakers</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13365,17 +13363,17 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="L123" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L123" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M123" s="7" t="n">
@@ -13392,16 +13390,16 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123" s="10" t="n">
         <v>1</v>
@@ -13409,15 +13407,15 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W123" s="10" t="n">
+      <c r="V123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="X123" s="10" t="n">
-        <v>5</v>
-      </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
@@ -13428,13 +13426,9 @@
         <v>1</v>
       </c>
       <c r="AB123" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC123" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="AC123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -13444,19 +13438,19 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>3549525</v>
+        <v>1095816</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Lyon English Toastmasters</t>
+          <t>Toulouse Toastmasters Communication</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13470,17 +13464,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>11</v>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M124" s="7" t="n">
@@ -13497,45 +13491,49 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W124" s="9" t="n">
-        <v>0</v>
+      <c r="V124" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W124" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB124" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC124" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC124" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -13549,15 +13547,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1850126</v>
+        <v>3549525</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Lyon Toastmasters Unlimited</t>
+          <t>Lyon English Toastmasters</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13571,17 +13569,17 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L125" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L125" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M125" s="7" t="n">
@@ -13598,7 +13596,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>0</v>
@@ -13609,20 +13607,20 @@
       <c r="S125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T125" s="10" t="n">
-        <v>1</v>
+      <c r="T125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
@@ -13634,13 +13632,9 @@
         <v>1</v>
       </c>
       <c r="AB125" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC125" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -13654,11 +13648,11 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7064056</v>
+        <v>1850126</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Annecy</t>
+          <t>Lyon Toastmasters Unlimited</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
@@ -13676,13 +13670,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
@@ -13703,7 +13697,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
@@ -13712,7 +13706,7 @@
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T126" s="10" t="n">
         <v>1</v>
@@ -13721,13 +13715,13 @@
         <v>0</v>
       </c>
       <c r="V126" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -13739,11 +13733,11 @@
         <v>1</v>
       </c>
       <c r="AB126" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC126" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -13759,15 +13753,15 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>28678901</v>
+        <v>7064056</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Club Valence</t>
+          <t>Toastmasters Annecy</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13781,17 +13775,17 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L127" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M127" s="7" t="n">
@@ -13817,36 +13811,40 @@
         <v>0</v>
       </c>
       <c r="S127" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U127" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X127" s="9" t="n">
-        <v>2</v>
+      <c r="X127" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z127" s="9" t="n">
-        <v>0</v>
+      <c r="Z127" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA127" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB127" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC127" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC127" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -13860,15 +13858,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1530443</v>
+        <v>28678901</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Grand Lyon</t>
+          <t>Toastmasters Club Valence</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13882,17 +13880,17 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K128" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L128" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L128" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M128" s="7" t="n">
@@ -13909,10 +13907,10 @@
         </is>
       </c>
       <c r="P128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13920,8 +13918,8 @@
       <c r="S128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T128" s="10" t="n">
-        <v>1</v>
+      <c r="T128" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U128" s="9" t="n">
         <v>0</v>
@@ -13932,8 +13930,8 @@
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X128" s="10" t="n">
-        <v>4</v>
+      <c r="X128" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
@@ -13945,13 +13943,9 @@
         <v>1</v>
       </c>
       <c r="AB128" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC128" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -13961,15 +13955,15 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>3657380</v>
+        <v>1530443</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Les Mots Passants</t>
+          <t>Toastmasters Grand Lyon</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -13987,10 +13981,10 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K129" s="4" t="n">
         <v>0</v>
@@ -14017,7 +14011,7 @@
         <v>1</v>
       </c>
       <c r="Q129" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R129" s="9" t="n">
         <v>0</v>
@@ -14038,7 +14032,7 @@
         <v>0</v>
       </c>
       <c r="X129" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y129" s="9" t="n">
         <v>0</v>
@@ -14050,9 +14044,13 @@
         <v>1</v>
       </c>
       <c r="AB129" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC129" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC129" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -14066,15 +14064,15 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>2753458</v>
+        <v>3657380</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Aix En Provence - Le Cours Des Mots</t>
+          <t>Les Mots Passants</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F130" s="6" t="n">
         <v>10</v>
@@ -14088,10 +14086,10 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K130" s="4" t="n">
         <v>0</v>
@@ -14115,7 +14113,7 @@
         </is>
       </c>
       <c r="P130" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q130" s="9" t="n">
         <v>0</v>
@@ -14126,8 +14124,8 @@
       <c r="S130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T130" s="9" t="n">
-        <v>0</v>
+      <c r="T130" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U130" s="9" t="n">
         <v>0</v>
@@ -14138,8 +14136,8 @@
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X130" s="9" t="n">
-        <v>2</v>
+      <c r="X130" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -14151,7 +14149,7 @@
         <v>1</v>
       </c>
       <c r="AB130" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC130" s="4" t="inlineStr"/>
     </row>
@@ -14167,15 +14165,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>28678465</v>
+        <v>2753458</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Grand Avignon</t>
+          <t>Toastmasters Aix En Provence - Le Cours Des Mots</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14189,10 +14187,10 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K131" s="4" t="n">
         <v>0</v>
@@ -14240,19 +14238,19 @@
         <v>0</v>
       </c>
       <c r="X131" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y131" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB131" s="4" t="n">
         <v>3</v>
-      </c>
-      <c r="Y131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA131" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB131" s="4" t="n">
-        <v>4</v>
       </c>
       <c r="AC131" s="4" t="inlineStr"/>
     </row>
@@ -14268,15 +14266,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>4750231</v>
+        <v>28678465</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Marseille</t>
+          <t>Toastmasters Grand Avignon</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14290,13 +14288,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14317,10 +14315,10 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R132" s="9" t="n">
         <v>0</v>
@@ -14328,20 +14326,20 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="10" t="n">
-        <v>1</v>
+      <c r="T132" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X132" s="10" t="n">
-        <v>4</v>
+      <c r="X132" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -14369,15 +14367,15 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>6666232</v>
+        <v>4750231</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Toulon</t>
+          <t>Toastmasters Marseille</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -14391,17 +14389,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="J133" s="4" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M133" s="7" t="n">
@@ -14418,7 +14416,7 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -14429,14 +14427,14 @@
       <c r="S133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14454,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC133" s="4" t="inlineStr"/>
     </row>
@@ -14466,15 +14464,15 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>7373921</v>
+        <v>6666232</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Eloquence Nice Toastmasters Club</t>
+          <t>Toastmasters Toulon</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
@@ -14492,17 +14490,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L134" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="7" t="n">
@@ -14537,31 +14535,27 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y134" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA134" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB134" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y134" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA134" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB134" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC134" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AC134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -14575,11 +14569,11 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>1387178</v>
+        <v>7373921</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Côte D'Azur</t>
+          <t>Eloquence Nice Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
@@ -14597,13 +14591,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -14642,13 +14636,13 @@
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14680,15 +14674,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>2677777</v>
+        <v>1387178</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters NICE</t>
+          <t>Toastmasters Côte D'Azur</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14702,10 +14696,10 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J136" s="4" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K136" s="4" t="n">
         <v>0</v>
@@ -14758,8 +14752,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14785,15 +14779,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>5038814</v>
+        <v>2677777</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Sophia Antipolis</t>
+          <t>Toastmasters NICE</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14807,10 +14801,10 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K137" s="4" t="n">
         <v>0</v>
@@ -14845,8 +14839,8 @@
       <c r="S137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T137" s="10" t="n">
-        <v>1</v>
+      <c r="T137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U137" s="9" t="n">
         <v>0</v>
@@ -14858,28 +14852,133 @@
         <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y137" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB137" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC137" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="n">
+        <v>5038814</v>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>Toastmasters Sophia Antipolis</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F138" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G138" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="J138" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K138" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M138" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O138" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y137" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA137" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB137" s="4" t="n">
+      <c r="Y138" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB138" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="AC137" s="4" t="inlineStr">
+      <c r="AC138" s="4" t="inlineStr">
         <is>
           <t>Select Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC137"/>
+  <autoFilter ref="A1:AC138"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14966,7 +15065,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -14999,7 +15098,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15032,7 +15131,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15065,7 +15164,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15098,7 +15197,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15131,7 +15230,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15164,7 +15263,7 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15194,16 +15293,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -15296,7 +15395,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15329,7 +15428,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15395,7 +15494,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -15560,7 +15659,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15626,7 +15725,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15725,7 +15824,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -15758,7 +15857,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -15791,7 +15890,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -15824,7 +15923,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -15857,7 +15956,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 16 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1282,13 +1282,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -1326,11 +1326,11 @@
       <c r="U6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>1</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>4</v>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-22</v>
+        <v>-6</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2041,11 +2041,11 @@
       <c r="U13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V13" s="9" t="n">
-        <v>0</v>
+      <c r="V13" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W13" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" s="9" t="n">
         <v>2</v>
@@ -2053,8 +2053,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>0</v>
       </c>
       <c r="S17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" s="9" t="n">
         <v>0</v>
@@ -2460,8 +2460,8 @@
       <c r="V17" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W17" s="9" t="n">
-        <v>3</v>
+      <c r="W17" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>4</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="Q18" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="9" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         <v>4</v>
       </c>
       <c r="W19" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X19" s="10" t="n">
         <v>5</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2728,17 +2728,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L20" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2772,8 +2772,8 @@
       <c r="U20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>1</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
         <v>0</v>
@@ -2938,13 +2938,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>4</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>4</v>
       </c>
       <c r="W27" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X27" s="9" t="n">
         <v>3</v>
@@ -4164,7 +4164,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4178,13 +4178,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>49</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4225,8 +4225,8 @@
       <c r="V34" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W34" s="9" t="n">
-        <v>3</v>
+      <c r="W34" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>7</v>
@@ -4388,13 +4388,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5142,8 +5142,8 @@
       <c r="P43" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" s="9" t="n">
-        <v>1</v>
+      <c r="Q43" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R43" s="9" t="n">
         <v>0</v>
@@ -5521,13 +5521,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6141,13 +6141,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
@@ -6188,8 +6188,8 @@
       <c r="V53" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W53" s="9" t="n">
-        <v>3</v>
+      <c r="W53" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="X53" s="9" t="n">
         <v>1</v>
@@ -6343,13 +6343,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="X57" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6694,7 +6694,7 @@
         <v>0</v>
       </c>
       <c r="S58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" s="9" t="n">
         <v>0</v>
@@ -7165,13 +7165,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -8197,13 +8197,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>0</v>
@@ -8454,7 +8454,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -9056,7 +9056,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>0</v>
@@ -10978,13 +10978,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>4</v>
       </c>
       <c r="W100" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>4</v>
@@ -11184,13 +11184,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
@@ -11481,7 +11481,7 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F105" s="6" t="n">
         <v>10</v>
@@ -11495,13 +11495,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11539,8 +11539,8 @@
       <c r="U105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V105" s="9" t="n">
-        <v>3</v>
+      <c r="V105" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11701,13 +11701,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -12342,10 +12342,10 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
@@ -12717,7 +12717,7 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12731,17 +12731,17 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L117" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M117" s="8" t="n">
@@ -12758,7 +12758,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>1</v>
@@ -12769,14 +12769,14 @@
       <c r="S117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T117" s="9" t="n">
-        <v>0</v>
+      <c r="T117" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V117" s="9" t="n">
-        <v>2</v>
+      <c r="V117" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12872,13 +12872,13 @@
         <v>0</v>
       </c>
       <c r="S118" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U118" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V118" s="10" t="n">
         <v>4</v>
@@ -13357,13 +13357,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X123" s="10" t="n">
         <v>7</v>
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13503,8 +13503,8 @@
       <c r="T124" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U124" s="9" t="n">
-        <v>0</v>
+      <c r="U124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V124" s="10" t="n">
         <v>4</v>
@@ -13563,13 +13563,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>4</v>
       </c>
       <c r="W125" s="10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>5</v>
@@ -13695,7 +13695,7 @@
         </is>
       </c>
       <c r="P126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q126" s="9" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F127" s="6" t="n">
         <v>10</v>
@@ -13769,13 +13769,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13816,8 +13816,8 @@
       <c r="V127" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W127" s="9" t="n">
-        <v>2</v>
+      <c r="W127" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X127" s="10" t="n">
         <v>7</v>
@@ -14286,13 +14286,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X132" s="9" t="n">
         <v>2</v>
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14728,8 +14728,8 @@
       <c r="S136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
@@ -15164,7 +15164,7 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15230,7 +15230,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15263,13 +15263,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -15278,7 +15278,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -15329,7 +15329,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15428,7 +15428,7 @@
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
@@ -15791,7 +15791,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -15857,7 +15857,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15872,7 +15872,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -15923,7 +15923,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -15956,13 +15956,13 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>

--- a/docs/d/59/inyear.xlsx
+++ b/docs/d/59/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1694,13 +1694,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-16</v>
+        <v>-12</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1738,11 +1738,11 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W10" s="9" t="n">
         <v>3</v>
-      </c>
-      <c r="W10" s="9" t="n">
-        <v>0</v>
       </c>
       <c r="X10" s="10" t="n">
         <v>4</v>
@@ -1795,13 +1795,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-19</v>
+        <v>-18</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>4</v>
       </c>
       <c r="W11" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X11" s="9" t="n">
         <v>3</v>
@@ -2203,13 +2203,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" s="9" t="n">
         <v>0</v>
@@ -2251,7 +2251,7 @@
         <v>4</v>
       </c>
       <c r="W15" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X15" s="10" t="n">
         <v>5</v>
@@ -2413,13 +2413,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>4</v>
       </c>
       <c r="W17" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>4</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2760,8 +2760,8 @@
       <c r="Q20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R20" s="9" t="n">
-        <v>0</v>
+      <c r="R20" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S20" s="9" t="n">
         <v>0</v>
@@ -2833,13 +2833,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>38</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="P21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>0</v>
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="V21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="9" t="n">
         <v>0</v>
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="P30" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q30" s="9" t="n">
         <v>1</v>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="6" t="n">
         <v>10</v>
@@ -3871,17 +3871,17 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-21</v>
-      </c>
-      <c r="L31" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M31" s="8" t="n">
@@ -3915,11 +3915,11 @@
       <c r="U31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="9" t="n">
-        <v>0</v>
+      <c r="V31" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W31" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X31" s="9" t="n">
         <v>2</v>
@@ -3950,11 +3950,11 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>28679421</v>
+        <v>28680209</v>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Mons Toastmasters Club</t>
+          <t>Lille English Toastmasters</t>
         </is>
       </c>
       <c r="E32" s="5" t="n">
@@ -3972,13 +3972,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -4017,26 +4017,24 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X32" s="10" t="n">
-        <v>7</v>
+      <c r="X32" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB32" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -4051,11 +4049,11 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>8953</v>
+        <v>28679421</v>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>SHAPE International Toastmasters Club</t>
+          <t>Mons Toastmasters Club</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
@@ -4073,17 +4071,17 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M33" s="8" t="n">
@@ -4100,7 +4098,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4118,13 +4116,13 @@
         <v>0</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W33" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X33" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33" s="9" t="n">
         <v>0</v>
@@ -4136,13 +4134,9 @@
         <v>1</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC33" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -4156,15 +4150,15 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1276679</v>
+        <v>8953</v>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Gent</t>
+          <t>SHAPE International Toastmasters Club</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -4178,17 +4172,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-12</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4205,7 +4199,7 @@
         </is>
       </c>
       <c r="P34" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q34" s="9" t="n">
         <v>0</v>
@@ -4214,7 +4208,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -4222,14 +4216,14 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W34" s="10" t="n">
-        <v>5</v>
+      <c r="V34" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W34" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X34" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y34" s="9" t="n">
         <v>0</v>
@@ -4241,7 +4235,7 @@
         <v>1</v>
       </c>
       <c r="AB34" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC34" s="4" t="inlineStr">
         <is>
@@ -4261,15 +4255,15 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2263308</v>
+        <v>1276679</v>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Lille</t>
+          <t>Toastmasters Gent</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4283,17 +4277,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L35" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-12</v>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4310,7 +4304,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4319,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="9" t="n">
         <v>0</v>
@@ -4327,14 +4321,14 @@
       <c r="U35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="W35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="9" t="n">
-        <v>2</v>
+      <c r="V35" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W35" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="X35" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y35" s="9" t="n">
         <v>0</v>
@@ -4346,11 +4340,11 @@
         <v>1</v>
       </c>
       <c r="AB35" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC35" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -4362,19 +4356,19 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>7761128</v>
+        <v>2263308</v>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Les Orateurs De Liege Toastmasters Club</t>
+          <t>Toastmasters Lille</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="6" t="n">
         <v>10</v>
@@ -4388,13 +4382,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J36" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4432,30 +4426,30 @@
       <c r="U36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V36" s="10" t="n">
-        <v>4</v>
+      <c r="V36" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X36" s="10" t="n">
+      <c r="X36" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="AC36" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -4471,15 +4465,15 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1458076</v>
+        <v>7761128</v>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>ToastMasterCard Club</t>
+          <t>Les Orateurs De Liege Toastmasters Club</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="6" t="n">
         <v>10</v>
@@ -4493,17 +4487,17 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J37" s="4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L37" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M37" s="8" t="n">
@@ -4537,14 +4531,14 @@
       <c r="U37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V37" s="9" t="n">
-        <v>0</v>
+      <c r="V37" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X37" s="9" t="n">
-        <v>2</v>
+      <c r="X37" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y37" s="9" t="n">
         <v>0</v>
@@ -4556,11 +4550,11 @@
         <v>1</v>
       </c>
       <c r="AB37" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AC37" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -4576,15 +4570,15 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1366750</v>
+        <v>1458076</v>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Fonske Leuven</t>
+          <t>ToastMasterCard Club</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4598,13 +4592,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J38" s="4" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4634,22 +4628,22 @@
         <v>0</v>
       </c>
       <c r="S38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T38" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X38" s="10" t="n">
-        <v>7</v>
+      <c r="X38" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y38" s="9" t="n">
         <v>0</v>
@@ -4661,11 +4655,11 @@
         <v>1</v>
       </c>
       <c r="AB38" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC38" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -4681,15 +4675,15 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1049050</v>
+        <v>1366750</v>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Hasselt</t>
+          <t>Toastmasters Fonske Leuven</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="6" t="n">
         <v>10</v>
@@ -4703,13 +4697,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J39" s="4" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-2</v>
+        <v>-14</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4730,7 +4724,7 @@
         </is>
       </c>
       <c r="P39" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q39" s="9" t="n">
         <v>0</v>
@@ -4739,22 +4733,22 @@
         <v>0</v>
       </c>
       <c r="S39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T39" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U39" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X39" s="9" t="n">
-        <v>3</v>
+      <c r="X39" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y39" s="9" t="n">
         <v>0</v>
@@ -4766,11 +4760,11 @@
         <v>1</v>
       </c>
       <c r="AB39" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AC39" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
@@ -4786,11 +4780,11 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>28679293</v>
+        <v>1049050</v>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters Namur</t>
+          <t>Toastmasters Hasselt</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -4808,17 +4802,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J40" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>-17</v>
-      </c>
-      <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4835,7 +4829,7 @@
         </is>
       </c>
       <c r="P40" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="9" t="n">
         <v>0</v>
@@ -4858,8 +4852,8 @@
       <c r="W40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X40" s="10" t="n">
-        <v>7</v>
+      <c r="X40" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y40" s="9" t="n">
         <v>0</v>
@@ -4871,7 +4865,7 @@
         <v>1</v>
       </c>
       <c r="AB40" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC40" s="4" t="inlineStr">
         <is>
@@ -4887,19 +4881,19 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>7761007</v>
+        <v>28679293</v>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Campus Speakers</t>
+          <t>Toastmasters Namur</t>
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="6" t="n">
         <v>10</v>
@@ -4913,13 +4907,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>-14</v>
+        <v>-17</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4958,27 +4952,31 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X41" s="9" t="n">
-        <v>0</v>
+      <c r="X41" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="n">
-        <v>0</v>
+      <c r="Z41" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA41" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC41" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -4992,15 +4990,15 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>28680209</v>
+        <v>7761007</v>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Lille English Toastmasters</t>
+          <t>Campus Speakers</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
         <v>10</v>
@@ -5014,17 +5012,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="J42" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -5070,13 +5068,15 @@
       <c r="Y42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z42" s="10" t="n">
+      <c r="Z42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="AA42" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5319,17 +5319,17 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M45" s="8" t="n">
@@ -5355,7 +5355,7 @@
         <v>0</v>
       </c>
       <c r="S45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T45" s="9" t="n">
         <v>0</v>
@@ -5363,11 +5363,11 @@
       <c r="U45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="9" t="n">
-        <v>2</v>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W45" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" s="9" t="n">
         <v>2</v>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q47" s="10" t="n">
         <v>2</v>
@@ -5727,13 +5727,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5772,7 +5772,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5832,13 +5832,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -6553,13 +6553,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X57" s="10" t="n">
         <v>7</v>
@@ -6862,13 +6862,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -8092,13 +8092,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8140,7 +8140,7 @@
         <v>4</v>
       </c>
       <c r="W72" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X72" s="10" t="n">
         <v>4</v>
@@ -9435,7 +9435,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9449,13 +9449,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9493,8 +9493,8 @@
       <c r="U85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="9" t="n">
-        <v>3</v>
+      <c r="V85" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9752,13 +9752,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>-13</v>
+        <v>-11</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -10463,13 +10463,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>-19</v>
+        <v>-15</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -11495,13 +11495,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>43</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
         <v>4</v>
       </c>
       <c r="W105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X105" s="10" t="n">
         <v>6</v>
@@ -11802,13 +11802,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -12251,8 +12251,8 @@
       <c r="T112" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U112" s="9" t="n">
-        <v>0</v>
+      <c r="U112" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V112" s="9" t="n">
         <v>1</v>
@@ -12315,13 +12315,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12363,7 +12363,7 @@
         <v>4</v>
       </c>
       <c r="W113" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X113" s="10" t="n">
         <v>6</v>
@@ -12521,13 +12521,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>54</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-20</v>
+        <v>-19</v>
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>4</v>
       </c>
       <c r="W115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X115" s="10" t="n">
         <v>5</v>
@@ -13032,7 +13032,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -13046,13 +13046,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
@@ -13090,11 +13090,11 @@
       <c r="U120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V120" s="9" t="n">
-        <v>3</v>
+      <c r="V120" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W120" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X120" s="10" t="n">
         <v>4</v>
@@ -13549,7 +13549,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13589,8 +13589,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P125" s="9" t="n">
-        <v>3</v>
+      <c r="P125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>1</v>
@@ -13769,13 +13769,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>4</v>
       </c>
       <c r="W127" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X127" s="10" t="n">
         <v>7</v>
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14690,13 +14690,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
@@ -14734,8 +14734,8 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>2</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -15197,7 +15197,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -15263,7 +15263,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -15326,16 +15326,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -15344,7 +15344,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -15392,16 +15392,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -15659,7 +15659,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15857,7 +15857,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15890,7 +15890,7 @@
         <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="E24" t="n">
         <v>2</v>
@@ -15923,13 +15923,13 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -16022,7 +16022,7 @@
         <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
